--- a/data/Test.xlsx
+++ b/data/Test.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,42 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>tag_key</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>tag_value</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>tag_key</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>tag_value</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>immunetag_key</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>immunetag_value</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>immunetag_key</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>immunetag_value</t>
+          <t>immunetag</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -469,70 +439,10 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>testobj_key</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>testobj_value</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>testobj_key</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>testobj_value</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>testobj_key</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>testobj_value</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>testobj_key</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testobj_value</t>
+          <t>testobj</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
         <is>
           <t>effect</t>
         </is>
@@ -546,42 +456,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>string</t>
+          <t>map&lt;string,string&gt;</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>string</t>
+          <t>map&lt;string,string&gt;</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -591,384 +471,157 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>uint32</t>
+          <t>repeated { uint32 key; uint32 value }</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
         <is>
           <t>uint32</t>
         </is>
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>map_key</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>map_value</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>map_key</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>map_value</t>
+          <t>common</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>map_key</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>map_value</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>map_key</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>map_value</t>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>message:testobj</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>message:testobj</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>message:testobj</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>message:testobj</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>message:testobj</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>message:testobj</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>message:testobj</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>message:testobj</t>
+          <t>common</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>repeated</t>
+          <t>common</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>common</t>
+    <row r="4"/>
+    <row r="5">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>免疫tag</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>等级</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>免疫tag</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>免疫tag</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>免疫tag</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>免疫tag</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -978,12 +631,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1002,19 +655,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1029,10 +682,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1049,11 +702,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1063,12 +716,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1120,25 +773,25 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1148,12 +801,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1187,10 +840,10 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1202,28 +855,28 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1233,12 +886,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1257,25 +910,25 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1287,10 +940,10 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1304,11 +957,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1318,12 +971,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1378,97 +1031,12 @@
         <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Wood</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>100</v>
-      </c>
-      <c r="K12" t="n">
-        <v>100</v>
-      </c>
-      <c r="L12" t="n">
-        <v>100</v>
-      </c>
-      <c r="M12" t="n">
-        <v>100</v>
-      </c>
-      <c r="N12" t="n">
-        <v>100</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/Test.xlsx
+++ b/data/Test.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>immunetag</t>
+          <t>immune_tag</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -512,7 +512,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="F5" t="inlineStr">
         <is>
